--- a/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-701_CALIFICADO.xlsx
@@ -8385,11 +8385,7 @@
           <t>KAROL SOFIA GUZMAN LOPEZ</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1030648404</t>
-        </is>
-      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="n">
         <v>7</v>
       </c>
@@ -8638,11 +8634,7 @@
           <t>KAROL SOFIA GUZMAN LOPEZ</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>1030648404</t>
-        </is>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="n">
         <v>7</v>
       </c>

--- a/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3329,11 +3289,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3582,11 +3538,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5100,11 +5032,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5353,11 +5281,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5606,11 +5530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5859,11 +5779,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6108,11 +6024,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6357,11 +6269,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6598,11 +6506,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6847,11 +6751,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7100,11 +7000,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7353,11 +7249,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7606,11 +7498,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7859,11 +7747,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8112,11 +7996,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8365,11 +8245,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8614,11 +8490,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8863,11 +8735,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9116,11 +8984,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9369,11 +9233,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9622,11 +9482,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9875,11 +9731,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10128,11 +9980,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10381,11 +10229,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10630,11 +10474,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10883,11 +10723,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11136,11 +10972,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11389,11 +11221,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11642,11 +11470,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11895,11 +11719,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12148,11 +11968,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12401,11 +12217,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12654,11 +12466,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12907,11 +12715,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13160,11 +12964,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13413,11 +13213,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13666,11 +13462,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13919,11 +13711,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14172,11 +13960,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14425,11 +14209,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14678,11 +14458,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14931,11 +14707,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15184,11 +14956,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15437,11 +15205,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15690,11 +15454,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15943,11 +15703,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16196,11 +15952,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16449,11 +16201,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16702,11 +16450,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16955,11 +16699,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -17208,11 +16948,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -17461,11 +17197,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -17714,11 +17446,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
